--- a/dataset/02.wo_Defects/race_condition.xlsx
+++ b/dataset/02.wo_Defects/race_condition.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pthread_mutex_t glb_1_mutex; pthread_mutex_t glb_2_mutex; int race_glb_1=5; int race_glb_2=3; int race_condition_002_gbl=0; pthread_mutex_t mutex_count; pthread_mutex_t count_mutex =PTHREAD_MUTEX_INITIALIZER; int x=0; pthread_mutex_t race_condition_004_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int race_condition_004_glb_data = 0; pthread_mutex_t race_condition_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int race_condition_005_glb_data = 0; pthread_mutex_t race_condition_006_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int race_condition_006_glb_data = 0; pthread_mutex_t race_condition_007_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float race_condition_007_glb_data = 1000.0; pthread_mutex_t race_condition_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t race_condition_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; float race_condition_008_glb_data = 1000.0; extern volatile int vflag; void race_condition_001() { pthread_t pthread1,pthread2; pthread_mutex_init(&amp;glb_1_mutex,NULL); pthread_mutex_init(&amp;glb_2_mutex,NULL); pthread_create(&amp;pthread1,NULL,race_condition_001_1,NULL); pthread_create(&amp;pthread2,NULL,race_condition_001_2,NULL); pthread_join(pthread1,NULL); pthread_join(pthread2,NULL); } void* race_condition_001_2() { while(1) { pthread_mutex_lock(&amp;glb_2_mutex); race_glb_1=2+race_glb_1; pthread_mutex_unlock(&amp;glb_2_mutex); if(race_glb_1&gt;50) { break; } } return NULL; } void* race_condition_001_1() { while(1) { pthread_mutex_lock(&amp;glb_1_mutex); if(race_glb_1==5) { race_glb_1++; /*Tool should not detect this line as error*/ /*No ERROR:Race condition*/ } pthread_mutex_unlock(&amp;glb_1_mutex); if(race_glb_1&gt;50) { break; } } return NULL; }</t>
+          <t>pthread_mutex_t glb_1_mutex; pthread_mutex_t glb_2_mutex; int race_glb_1=5; int race_glb_2=3; int race_condition_002_gbl=0; pthread_mutex_t mutex_count; pthread_mutex_t count_mutex =PTHREAD_MUTEX_INITIALIZER; int x=0; pthread_mutex_t race_condition_004_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int race_condition_004_glb_data = 0; pthread_mutex_t race_condition_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int race_condition_005_glb_data = 0; pthread_mutex_t race_condition_006_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int race_condition_006_glb_data = 0; pthread_mutex_t race_condition_007_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float race_condition_007_glb_data = 1000.0; pthread_mutex_t race_condition_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t race_condition_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; float race_condition_008_glb_data = 1000.0; extern volatile int vflag; void race_condition_001() { pthread_t pthread1,pthread2; pthread_mutex_init(&amp;glb_1_mutex,NULL); pthread_mutex_init(&amp;glb_2_mutex,NULL); pthread_create(&amp;pthread1,NULL,race_condition_001_1,NULL); pthread_create(&amp;pthread2,NULL,race_condition_001_2,NULL); pthread_join(pthread1,NULL); pthread_join(pthread2,NULL); } void* race_condition_001_1() { while(1) { pthread_mutex_lock(&amp;glb_1_mutex); if(race_glb_1==5) { race_glb_1++; /*Tool should not detect this line as error*/ /*No ERROR:Race condition*/ } pthread_mutex_unlock(&amp;glb_1_mutex); if(race_glb_1&gt;50) { break; } } return NULL; } void* race_condition_001_2() { while(1) { pthread_mutex_lock(&amp;glb_2_mutex); race_glb_1=2+race_glb_1; pthread_mutex_unlock(&amp;glb_2_mutex); if(race_glb_1&gt;50) { break; } } return NULL; }</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
